--- a/output/pdf_financials_xlsx/ERTH.xlsx
+++ b/output/pdf_financials_xlsx/ERTH.xlsx
@@ -1964,13 +1964,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.336565</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.448248</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.101205</v>
       </c>
     </row>
     <row r="93">
@@ -3303,7 +3303,11 @@
           <t>Share-based payment reserve 16</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>1.336565</v>
       </c>

--- a/output/pdf_financials_xlsx/ERTH.xlsx
+++ b/output/pdf_financials_xlsx/ERTH.xlsx
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.037599</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.119897</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.29946</v>
       </c>
     </row>
     <row r="35">
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.037599</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.119897</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.29946</v>
       </c>
     </row>
     <row r="37">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/ERTH.xlsx
+++ b/output/pdf_financials_xlsx/ERTH.xlsx
@@ -672,20 +672,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-4.269333</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-8.642716</v>
       </c>
     </row>
     <row r="17">
@@ -754,20 +748,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-4.269333</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-8.642716</v>
       </c>
     </row>
     <row r="21">
@@ -808,20 +796,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-4.269333</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-8.642716</v>
       </c>
     </row>
     <row r="24">
@@ -896,20 +878,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-4.269333</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-8.642716</v>
       </c>
     </row>
     <row r="28">
@@ -934,20 +910,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>2.284778</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-2.068334</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-6.386664</v>
       </c>
     </row>
     <row r="30">
@@ -956,20 +926,14 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>16.41563866164412</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-29.98133426992962</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-93.72809117183742</v>
       </c>
     </row>
     <row r="31">
@@ -978,20 +942,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1000,20 +958,14 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>0.6048870476360584</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-61.8857011404548</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-126.8369955301074</v>
       </c>
     </row>
     <row r="33">
@@ -1126,13 +1078,13 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0</v>
+        <v>0.085429</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.071867</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.080482</v>
       </c>
     </row>
     <row r="41">
@@ -1142,13 +1094,13 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>4.379367</v>
+        <v>4.464796</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.643519</v>
+        <v>1.715386</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1.527928</v>
+        <v>1.60841</v>
       </c>
     </row>
     <row r="42">
@@ -1516,13 +1468,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>5.168099</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>4.348518</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>4.144115</v>
       </c>
     </row>
     <row r="65">
@@ -2066,20 +2018,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0.08419</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-4.269333</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-8.642716</v>
       </c>
     </row>
     <row r="100">
@@ -2201,13 +2147,13 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>0.29259</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>0.152963</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.178294</v>
       </c>
     </row>
     <row r="108">
@@ -2255,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.294275</v>
       </c>
     </row>
     <row r="111">
@@ -3156,7 +3102,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.626268</v>
       </c>
@@ -3458,7 +3408,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.08419</v>
       </c>
@@ -3545,7 +3499,11 @@
           <t>Deferred tax expense (recovery) 13</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>-0.608</v>
       </c>
@@ -3630,7 +3588,11 @@
           <t>Accretion 20</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -3746,7 +3708,11 @@
           <t>Share-based compensation expense 16</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.29259</v>
       </c>
@@ -4067,7 +4033,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4927,7 +4897,11 @@
           <t>Net Earnings (Loss)</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E74" s="5" t="n">
         <v>0.08419</v>
       </c>
